--- a/demo-files/tata-capital-bulk-filing-template.xlsx
+++ b/demo-files/tata-capital-bulk-filing-template.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Cases" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Extra cheques" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="339">
   <si>
     <t>Case reference</t>
   </si>
@@ -53,6 +52,21 @@
     <t>Person responsible designation</t>
   </si>
   <si>
+    <t>Person responsible mobile</t>
+  </si>
+  <si>
+    <t>Person responsible email</t>
+  </si>
+  <si>
+    <t>Person responsible address</t>
+  </si>
+  <si>
+    <t>Person responsible city</t>
+  </si>
+  <si>
+    <t>Person responsible pincode</t>
+  </si>
+  <si>
     <t>Cheque number</t>
   </si>
   <si>
@@ -83,6 +97,9 @@
     <t>Complainant branch IFSC</t>
   </si>
   <si>
+    <t>Complainant branch police station</t>
+  </si>
+  <si>
     <t>Drawer branch police station</t>
   </si>
   <si>
@@ -122,6 +139,153 @@
     <t>Reason for condonation of delay</t>
   </si>
   <si>
+    <t>Additional details</t>
+  </si>
+  <si>
+    <t>Witness name</t>
+  </si>
+  <si>
+    <t>Witness designation</t>
+  </si>
+  <si>
+    <t>Witness age</t>
+  </si>
+  <si>
+    <t>What the witness will prove</t>
+  </si>
+  <si>
+    <t>Witness mobile</t>
+  </si>
+  <si>
+    <t>Witness email</t>
+  </si>
+  <si>
+    <t>Witness address</t>
+  </si>
+  <si>
+    <t>Witness city</t>
+  </si>
+  <si>
+    <t>Witness pincode</t>
+  </si>
+  <si>
+    <t>Other pending case court</t>
+  </si>
+  <si>
+    <t>Other pending case number</t>
+  </si>
+  <si>
+    <t>Complainant type_2</t>
+  </si>
+  <si>
+    <t>Complainant name_2</t>
+  </si>
+  <si>
+    <t>Complainant institution type_2</t>
+  </si>
+  <si>
+    <t>Complainant CIN or PAN_2</t>
+  </si>
+  <si>
+    <t>Complainant age_2</t>
+  </si>
+  <si>
+    <t>Complainant gender_2</t>
+  </si>
+  <si>
+    <t>Complainant mobile_2</t>
+  </si>
+  <si>
+    <t>Complainant email_2</t>
+  </si>
+  <si>
+    <t>Complainant address_2</t>
+  </si>
+  <si>
+    <t>Complainant city_2</t>
+  </si>
+  <si>
+    <t>Complainant pincode_2</t>
+  </si>
+  <si>
+    <t>Complainant representative name_2</t>
+  </si>
+  <si>
+    <t>Complainant representative designation_2</t>
+  </si>
+  <si>
+    <t>Complainant representative age_2</t>
+  </si>
+  <si>
+    <t>Complainant representative mobile_2</t>
+  </si>
+  <si>
+    <t>Cheque number_2</t>
+  </si>
+  <si>
+    <t>Cheque date_2</t>
+  </si>
+  <si>
+    <t>Cheque amount_2</t>
+  </si>
+  <si>
+    <t>Drawer bank IFSC_2</t>
+  </si>
+  <si>
+    <t>Drawer account number_2</t>
+  </si>
+  <si>
+    <t>Presentation date_2</t>
+  </si>
+  <si>
+    <t>Return date_2</t>
+  </si>
+  <si>
+    <t>Return reason_2</t>
+  </si>
+  <si>
+    <t>Accused type_2</t>
+  </si>
+  <si>
+    <t>Accused name_2</t>
+  </si>
+  <si>
+    <t>Accused age_2</t>
+  </si>
+  <si>
+    <t>Accused mobile_2</t>
+  </si>
+  <si>
+    <t>Accused address_2</t>
+  </si>
+  <si>
+    <t>Accused city_2</t>
+  </si>
+  <si>
+    <t>Accused pincode_2</t>
+  </si>
+  <si>
+    <t>Witness name_2</t>
+  </si>
+  <si>
+    <t>Witness designation_2</t>
+  </si>
+  <si>
+    <t>What the witness will prove_2</t>
+  </si>
+  <si>
+    <t>Witness mobile_2</t>
+  </si>
+  <si>
+    <t>Witness address_2</t>
+  </si>
+  <si>
+    <t>Witness city_2</t>
+  </si>
+  <si>
+    <t>Witness pincode_2</t>
+  </si>
+  <si>
     <t>Text. Required, unique in the file</t>
   </si>
   <si>
@@ -137,10 +301,10 @@
     <t>Number, no commas. Optional</t>
   </si>
   <si>
-    <t>10-digit mobile number. Mobile or email</t>
-  </si>
-  <si>
-    <t>Text. Mobile or email</t>
+    <t>10-digit mobile number. Required: mobile or email</t>
+  </si>
+  <si>
+    <t>Text. Required: mobile or email</t>
   </si>
   <si>
     <t>Text. Optional</t>
@@ -149,6 +313,9 @@
     <t>Text. Required when Institution</t>
   </si>
   <si>
+    <t>10-digit mobile number. Required when Institution</t>
+  </si>
+  <si>
     <t>Text. Required, 6 digits</t>
   </si>
   <si>
@@ -188,6 +355,33 @@
     <t>Text. Required when the system computes a delay</t>
   </si>
   <si>
+    <t>Text. Required: name or designation, for each witness</t>
+  </si>
+  <si>
+    <t>10-digit mobile number. Optional</t>
+  </si>
+  <si>
+    <t>Text. Required for each witness</t>
+  </si>
+  <si>
+    <t>Choose: Individual / Institution. Required for each further complainant</t>
+  </si>
+  <si>
+    <t>Text. Required for each further complainant</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required when Individual</t>
+  </si>
+  <si>
+    <t>Choose: Male / Female / Other. Optional</t>
+  </si>
+  <si>
+    <t>10-digit mobile number. Required when Individual</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required when Institution</t>
+  </si>
+  <si>
     <t>EXAMPLE-0001</t>
   </si>
   <si>
@@ -317,6 +511,24 @@
     <t>01-10-2026</t>
   </si>
   <si>
+    <t>Kunal S. Shah</t>
+  </si>
+  <si>
+    <t>Branch Manager, Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>The loan account statement and the dishonour</t>
+  </si>
+  <si>
+    <t>9879055501</t>
+  </si>
+  <si>
+    <t>Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>380009</t>
+  </si>
+  <si>
     <t>TCL-AHD-PL-1002</t>
   </si>
   <si>
@@ -422,6 +634,15 @@
     <t>29-09-2026</t>
   </si>
   <si>
+    <t>Kusum P. Solanki</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>9879012313</t>
+  </si>
+  <si>
     <t>TCL-AHD-PL-1004</t>
   </si>
   <si>
@@ -575,6 +796,21 @@
     <t>03-10-2026</t>
   </si>
   <si>
+    <t>The loan account statement</t>
+  </si>
+  <si>
+    <t>Dipti R. Vora</t>
+  </si>
+  <si>
+    <t>Collections Officer</t>
+  </si>
+  <si>
+    <t>Presentation and return of the cheque</t>
+  </si>
+  <si>
+    <t>9879055502</t>
+  </si>
+  <si>
     <t>TCL-AHD-PL-1007</t>
   </si>
   <si>
@@ -593,6 +829,9 @@
     <t>9, Sahjanand Park, Paldi</t>
   </si>
   <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
     <t>380006</t>
   </si>
   <si>
@@ -677,10 +916,19 @@
     <t>RG25366011IN</t>
   </si>
   <si>
+    <t>SARAS Court, Ahmedabad</t>
+  </si>
+  <si>
+    <t>eCC/2210/2026</t>
+  </si>
+  <si>
+    <t>253661</t>
+  </si>
+  <si>
     <t>TCL-AHD-PL-1010</t>
   </si>
   <si>
-    <t>Rupal H. Chauhan</t>
+    <t>Shree Ganesh Traders</t>
   </si>
   <si>
     <t>36</t>
@@ -689,15 +937,12 @@
     <t>9879012310</t>
   </si>
   <si>
-    <t>rupal.chauhan@mail.example</t>
+    <t>ganesh.traders@mail.example</t>
   </si>
   <si>
     <t>18, Nilkanth Society, Navrangpura</t>
   </si>
   <si>
-    <t>380009</t>
-  </si>
-  <si>
     <t>Navrangpura Police Station</t>
   </si>
   <si>
@@ -783,9 +1028,6 @@
   </si>
   <si>
     <t>RG33187611IN</t>
-  </si>
-  <si>
-    <t>253661</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:CM15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -1195,28 +1437,78 @@
     <col min="11" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="27" customWidth="1"/>
     <col min="13" max="13" width="34" customWidth="1"/>
-    <col min="14" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="25" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="42" customWidth="1"/>
-    <col min="23" max="23" width="27" customWidth="1"/>
-    <col min="24" max="24" width="32" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="24" customWidth="1"/>
-    <col min="27" max="28" width="26" customWidth="1"/>
-    <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="30" width="24" customWidth="1"/>
-    <col min="31" max="31" width="22" customWidth="1"/>
-    <col min="32" max="32" width="27" customWidth="1"/>
-    <col min="33" max="33" width="19" customWidth="1"/>
-    <col min="34" max="34" width="24" customWidth="1"/>
-    <col min="35" max="35" width="18" customWidth="1"/>
-    <col min="36" max="36" width="35" customWidth="1"/>
+    <col min="14" max="14" width="29" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="27" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1"/>
+    <col min="25" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="42" customWidth="1"/>
+    <col min="28" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="37" customWidth="1"/>
+    <col min="30" max="30" width="32" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="32" max="32" width="24" customWidth="1"/>
+    <col min="33" max="34" width="26" customWidth="1"/>
+    <col min="35" max="35" width="20" customWidth="1"/>
+    <col min="36" max="36" width="24" customWidth="1"/>
+    <col min="37" max="37" width="22" customWidth="1"/>
+    <col min="38" max="38" width="27" customWidth="1"/>
+    <col min="39" max="39" width="19" customWidth="1"/>
+    <col min="40" max="40" width="24" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="35" customWidth="1"/>
+    <col min="43" max="43" width="22" customWidth="1"/>
+    <col min="44" max="44" width="18" customWidth="1"/>
+    <col min="45" max="45" width="23" customWidth="1"/>
+    <col min="46" max="46" width="18" customWidth="1"/>
+    <col min="47" max="47" width="31" customWidth="1"/>
+    <col min="48" max="49" width="18" customWidth="1"/>
+    <col min="50" max="50" width="19" customWidth="1"/>
+    <col min="51" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="19" customWidth="1"/>
+    <col min="53" max="53" width="28" customWidth="1"/>
+    <col min="54" max="54" width="29" customWidth="1"/>
+    <col min="55" max="56" width="22" customWidth="1"/>
+    <col min="57" max="57" width="34" customWidth="1"/>
+    <col min="58" max="58" width="28" customWidth="1"/>
+    <col min="59" max="59" width="21" customWidth="1"/>
+    <col min="60" max="61" width="24" customWidth="1"/>
+    <col min="62" max="62" width="23" customWidth="1"/>
+    <col min="63" max="63" width="25" customWidth="1"/>
+    <col min="64" max="64" width="22" customWidth="1"/>
+    <col min="65" max="65" width="25" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="44" customWidth="1"/>
+    <col min="68" max="68" width="36" customWidth="1"/>
+    <col min="69" max="69" width="39" customWidth="1"/>
+    <col min="70" max="70" width="19" customWidth="1"/>
+    <col min="71" max="71" width="18" customWidth="1"/>
+    <col min="72" max="72" width="19" customWidth="1"/>
+    <col min="73" max="73" width="22" customWidth="1"/>
+    <col min="74" max="74" width="27" customWidth="1"/>
+    <col min="75" max="75" width="23" customWidth="1"/>
+    <col min="76" max="76" width="18" customWidth="1"/>
+    <col min="77" max="77" width="19" customWidth="1"/>
+    <col min="78" max="80" width="18" customWidth="1"/>
+    <col min="81" max="81" width="20" customWidth="1"/>
+    <col min="82" max="82" width="21" customWidth="1"/>
+    <col min="83" max="83" width="18" customWidth="1"/>
+    <col min="84" max="84" width="21" customWidth="1"/>
+    <col min="85" max="85" width="18" customWidth="1"/>
+    <col min="86" max="86" width="25" customWidth="1"/>
+    <col min="87" max="87" width="33" customWidth="1"/>
+    <col min="88" max="88" width="20" customWidth="1"/>
+    <col min="89" max="89" width="21" customWidth="1"/>
+    <col min="90" max="90" width="18" customWidth="1"/>
+    <col min="91" max="91" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1325,1621 +1617,2016 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>57</v>
+        <v>108</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BH2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BI2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BJ2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BK2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BO2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BR2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BS2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BV2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BW2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BY2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="CA2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="CB2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="CC2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="CD2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="CE2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="CF2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="CG2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="CH2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="CI2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="CJ2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="CK2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CL2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CM2" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>61</v>
+        <v>148</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BP3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="L4" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="M4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s">
-        <v>93</v>
-      </c>
-      <c r="O4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P4">
+        <v>126</v>
+      </c>
+      <c r="S4" t="s">
+        <v>158</v>
+      </c>
+      <c r="T4" t="s">
+        <v>159</v>
+      </c>
+      <c r="U4">
         <v>148500</v>
       </c>
-      <c r="Q4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R4" t="s">
-        <v>95</v>
-      </c>
-      <c r="S4" t="s">
-        <v>96</v>
-      </c>
-      <c r="T4" t="s">
-        <v>97</v>
-      </c>
-      <c r="U4" t="s">
-        <v>76</v>
-      </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="W4" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="X4" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="Z4" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="AA4" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AB4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="AE4" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="AF4" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="AG4" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AH4" t="s">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="AI4" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="AJ4" t="s">
-        <v>61</v>
+        <v>165</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="J5" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="K5" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="L5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5" t="s">
-        <v>108</v>
-      </c>
-      <c r="O5" t="s">
-        <v>109</v>
-      </c>
-      <c r="P5">
+        <v>126</v>
+      </c>
+      <c r="S5" t="s">
+        <v>179</v>
+      </c>
+      <c r="T5" t="s">
+        <v>180</v>
+      </c>
+      <c r="U5">
         <v>92750</v>
       </c>
-      <c r="Q5" t="s">
-        <v>110</v>
-      </c>
-      <c r="R5" t="s">
-        <v>111</v>
-      </c>
-      <c r="S5" t="s">
-        <v>112</v>
-      </c>
-      <c r="T5" t="s">
-        <v>113</v>
-      </c>
-      <c r="U5" t="s">
-        <v>76</v>
-      </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="W5" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="X5" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="Z5" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="AA5" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AB5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="AE5" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="AF5" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="AG5" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AH5" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="AI5" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="AJ5" t="s">
-        <v>61</v>
+        <v>187</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="H6" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="J6" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="K6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M6" t="s">
+        <v>126</v>
+      </c>
+      <c r="S6" t="s">
+        <v>196</v>
+      </c>
+      <c r="T6" t="s">
+        <v>197</v>
+      </c>
+      <c r="U6">
+        <v>365000</v>
+      </c>
+      <c r="V6" t="s">
+        <v>198</v>
+      </c>
+      <c r="W6" t="s">
+        <v>199</v>
+      </c>
+      <c r="X6" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>126</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>124</v>
       </c>
-      <c r="L6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6" t="s">
-        <v>125</v>
-      </c>
-      <c r="O6" t="s">
-        <v>126</v>
-      </c>
-      <c r="P6">
-        <v>365000</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>127</v>
-      </c>
-      <c r="R6" t="s">
-        <v>128</v>
-      </c>
-      <c r="S6" t="s">
-        <v>129</v>
-      </c>
-      <c r="T6" t="s">
-        <v>130</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="CA6" t="s">
+        <v>207</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>208</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>209</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>193</v>
+      </c>
+      <c r="CE6" t="s">
         <v>131</v>
       </c>
-      <c r="V6" t="s">
-        <v>77</v>
-      </c>
-      <c r="W6" t="s">
-        <v>78</v>
-      </c>
-      <c r="X6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA6" t="s">
+      <c r="CF6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" t="s">
+        <v>131</v>
+      </c>
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" t="s">
+        <v>126</v>
+      </c>
+      <c r="S7" t="s">
+        <v>218</v>
+      </c>
+      <c r="T7" t="s">
+        <v>219</v>
+      </c>
+      <c r="U7">
+        <v>76400</v>
+      </c>
+      <c r="V7" t="s">
+        <v>220</v>
+      </c>
+      <c r="W7" t="s">
+        <v>221</v>
+      </c>
+      <c r="X7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>224</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>225</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" t="s">
+        <v>233</v>
+      </c>
+      <c r="K8" t="s">
+        <v>234</v>
+      </c>
+      <c r="L8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s">
+        <v>126</v>
+      </c>
+      <c r="S8" t="s">
+        <v>235</v>
+      </c>
+      <c r="T8" t="s">
+        <v>236</v>
+      </c>
+      <c r="U8">
+        <v>58900</v>
+      </c>
+      <c r="V8" t="s">
+        <v>237</v>
+      </c>
+      <c r="W8" t="s">
+        <v>238</v>
+      </c>
+      <c r="X8" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" t="s">
+        <v>233</v>
+      </c>
+      <c r="K9" t="s">
+        <v>234</v>
+      </c>
+      <c r="L9" t="s">
+        <v>251</v>
+      </c>
+      <c r="M9" t="s">
+        <v>252</v>
+      </c>
+      <c r="S9" t="s">
+        <v>253</v>
+      </c>
+      <c r="T9" t="s">
+        <v>254</v>
+      </c>
+      <c r="U9">
+        <v>512000</v>
+      </c>
+      <c r="V9" t="s">
+        <v>255</v>
+      </c>
+      <c r="W9" t="s">
+        <v>256</v>
+      </c>
+      <c r="X9" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>258</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>204</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>261</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>171</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>262</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>263</v>
+      </c>
+      <c r="CI9" t="s">
+        <v>264</v>
+      </c>
+      <c r="CJ9" t="s">
+        <v>265</v>
+      </c>
+      <c r="CK9" t="s">
+        <v>170</v>
+      </c>
+      <c r="CL9" t="s">
+        <v>131</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" t="s">
+        <v>269</v>
+      </c>
+      <c r="G10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I10" t="s">
+        <v>272</v>
+      </c>
+      <c r="J10" t="s">
+        <v>273</v>
+      </c>
+      <c r="K10" t="s">
+        <v>274</v>
+      </c>
+      <c r="L10" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" t="s">
+        <v>126</v>
+      </c>
+      <c r="S10" t="s">
+        <v>275</v>
+      </c>
+      <c r="T10" t="s">
+        <v>159</v>
+      </c>
+      <c r="U10">
+        <v>133250</v>
+      </c>
+      <c r="V10" t="s">
+        <v>276</v>
+      </c>
+      <c r="W10" t="s">
+        <v>277</v>
+      </c>
+      <c r="X10" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>279</v>
+      </c>
+      <c r="AO10">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F11" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" t="s">
+        <v>284</v>
+      </c>
+      <c r="H11" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" t="s">
         <v>133</v>
       </c>
-      <c r="AB6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>61</v>
+      <c r="L11" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" t="s">
+        <v>126</v>
+      </c>
+      <c r="S11" t="s">
+        <v>287</v>
+      </c>
+      <c r="T11" t="s">
+        <v>180</v>
+      </c>
+      <c r="U11">
+        <v>64800</v>
+      </c>
+      <c r="V11" t="s">
+        <v>288</v>
+      </c>
+      <c r="W11" t="s">
+        <v>289</v>
+      </c>
+      <c r="X11" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>187</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="12" spans="1:77" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" t="s">
+        <v>294</v>
+      </c>
+      <c r="G12" t="s">
+        <v>295</v>
+      </c>
+      <c r="H12" t="s">
+        <v>296</v>
+      </c>
+      <c r="I12" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" t="s">
+        <v>297</v>
+      </c>
+      <c r="K12" t="s">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" t="s">
+        <v>126</v>
+      </c>
+      <c r="S12" t="s">
+        <v>298</v>
+      </c>
+      <c r="T12" t="s">
+        <v>197</v>
+      </c>
+      <c r="U12">
+        <v>214000</v>
+      </c>
+      <c r="V12" t="s">
+        <v>181</v>
+      </c>
+      <c r="W12" t="s">
+        <v>299</v>
+      </c>
+      <c r="X12" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>204</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>300</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>301</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>302</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>303</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>197</v>
+      </c>
+      <c r="BT12">
+        <v>120000</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>181</v>
+      </c>
+      <c r="BV12" t="s">
+        <v>299</v>
+      </c>
+      <c r="BW12" t="s">
+        <v>200</v>
+      </c>
+      <c r="BX12" t="s">
+        <v>201</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" t="s">
+        <v>308</v>
+      </c>
+      <c r="H13" t="s">
+        <v>309</v>
+      </c>
+      <c r="I13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K13" t="s">
+        <v>310</v>
+      </c>
+      <c r="L13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" t="s">
+        <v>126</v>
+      </c>
+      <c r="S13" t="s">
+        <v>311</v>
+      </c>
+      <c r="T13" t="s">
+        <v>219</v>
+      </c>
+      <c r="U13">
+        <v>87300</v>
+      </c>
+      <c r="V13" t="s">
         <v>137</v>
       </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="W13" t="s">
+        <v>312</v>
+      </c>
+      <c r="X13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z13" t="s">
         <v>141</v>
       </c>
-      <c r="I7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="AA13" t="s">
         <v>142</v>
       </c>
-      <c r="K7" t="s">
+      <c r="AB13" t="s">
         <v>143</v>
       </c>
-      <c r="L7" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" t="s">
-        <v>61</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="AE13" t="s">
         <v>144</v>
       </c>
-      <c r="O7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P7">
-        <v>76400</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="AF13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AG13" t="s">
         <v>146</v>
       </c>
-      <c r="R7" t="s">
-        <v>147</v>
-      </c>
-      <c r="S7" t="s">
-        <v>130</v>
-      </c>
-      <c r="T7" t="s">
-        <v>148</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="AH13" t="s">
+        <v>313</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G14" t="s">
+        <v>318</v>
+      </c>
+      <c r="H14" t="s">
+        <v>319</v>
+      </c>
+      <c r="I14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" t="s">
+        <v>320</v>
+      </c>
+      <c r="K14" t="s">
+        <v>321</v>
+      </c>
+      <c r="L14" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" t="s">
+        <v>126</v>
+      </c>
+      <c r="S14" t="s">
+        <v>322</v>
+      </c>
+      <c r="T14" t="s">
+        <v>236</v>
+      </c>
+      <c r="U14">
+        <v>69900</v>
+      </c>
+      <c r="V14" t="s">
+        <v>198</v>
+      </c>
+      <c r="W14" t="s">
+        <v>323</v>
+      </c>
+      <c r="X14" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>324</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>325</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>242</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM14" t="s">
         <v>149</v>
       </c>
-      <c r="V7" t="s">
-        <v>77</v>
-      </c>
-      <c r="W7" t="s">
-        <v>78</v>
-      </c>
-      <c r="X7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AN14" t="s">
         <v>150</v>
       </c>
-      <c r="AA7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>61</v>
+      <c r="AO14" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H8" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" t="s">
-        <v>161</v>
-      </c>
-      <c r="O8" t="s">
-        <v>162</v>
-      </c>
-      <c r="P8">
-        <v>58900</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>163</v>
-      </c>
-      <c r="R8" t="s">
-        <v>164</v>
-      </c>
-      <c r="S8" t="s">
-        <v>165</v>
-      </c>
-      <c r="T8" t="s">
-        <v>96</v>
-      </c>
-      <c r="U8" t="s">
-        <v>76</v>
-      </c>
-      <c r="V8" t="s">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s">
-        <v>78</v>
-      </c>
-      <c r="X8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" t="s">
-        <v>160</v>
-      </c>
-      <c r="L9" t="s">
-        <v>177</v>
-      </c>
-      <c r="M9" t="s">
-        <v>178</v>
-      </c>
-      <c r="N9" t="s">
-        <v>179</v>
-      </c>
-      <c r="O9" t="s">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" t="s">
+        <v>328</v>
+      </c>
+      <c r="E15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" t="s">
+        <v>329</v>
+      </c>
+      <c r="G15" t="s">
+        <v>330</v>
+      </c>
+      <c r="H15" t="s">
+        <v>331</v>
+      </c>
+      <c r="I15" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" t="s">
+        <v>332</v>
+      </c>
+      <c r="K15" t="s">
+        <v>333</v>
+      </c>
+      <c r="L15" t="s">
+        <v>334</v>
+      </c>
+      <c r="M15" t="s">
+        <v>335</v>
+      </c>
+      <c r="S15" t="s">
+        <v>336</v>
+      </c>
+      <c r="T15" t="s">
         <v>180</v>
       </c>
-      <c r="P9">
-        <v>512000</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>181</v>
-      </c>
-      <c r="R9" t="s">
-        <v>182</v>
-      </c>
-      <c r="S9" t="s">
-        <v>113</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="U15">
+        <v>289500</v>
+      </c>
+      <c r="V15" t="s">
+        <v>220</v>
+      </c>
+      <c r="W15" t="s">
+        <v>337</v>
+      </c>
+      <c r="X15" t="s">
         <v>183</v>
       </c>
-      <c r="U9" t="s">
-        <v>76</v>
-      </c>
-      <c r="V9" t="s">
-        <v>77</v>
-      </c>
-      <c r="W9" t="s">
-        <v>78</v>
-      </c>
-      <c r="X9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="Y15" t="s">
         <v>184</v>
       </c>
-      <c r="AA9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB9" t="s">
+      <c r="Z15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF15" t="s">
         <v>185</v>
       </c>
-      <c r="AC9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="AG15" t="s">
+        <v>204</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>338</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>187</v>
       </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H10" t="s">
-        <v>192</v>
-      </c>
-      <c r="I10" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" t="s">
-        <v>193</v>
-      </c>
-      <c r="K10" t="s">
-        <v>194</v>
-      </c>
-      <c r="L10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" t="s">
-        <v>195</v>
-      </c>
-      <c r="O10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10">
-        <v>133250</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>196</v>
-      </c>
-      <c r="R10" t="s">
-        <v>197</v>
-      </c>
-      <c r="S10" t="s">
-        <v>96</v>
-      </c>
-      <c r="T10" t="s">
-        <v>97</v>
-      </c>
-      <c r="U10" t="s">
-        <v>76</v>
-      </c>
-      <c r="V10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W10" t="s">
-        <v>78</v>
-      </c>
-      <c r="X10" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>198</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>199</v>
-      </c>
-      <c r="AI10">
-        <v>25000</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>202</v>
-      </c>
-      <c r="F11" t="s">
-        <v>203</v>
-      </c>
-      <c r="G11" t="s">
-        <v>204</v>
-      </c>
-      <c r="H11" t="s">
-        <v>205</v>
-      </c>
-      <c r="I11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" t="s">
-        <v>206</v>
-      </c>
-      <c r="K11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" t="s">
-        <v>207</v>
-      </c>
-      <c r="O11" t="s">
-        <v>109</v>
-      </c>
-      <c r="P11">
-        <v>64800</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>208</v>
-      </c>
-      <c r="R11" t="s">
-        <v>209</v>
-      </c>
-      <c r="S11" t="s">
-        <v>112</v>
-      </c>
-      <c r="T11" t="s">
-        <v>113</v>
-      </c>
-      <c r="U11" t="s">
-        <v>76</v>
-      </c>
-      <c r="V11" t="s">
-        <v>77</v>
-      </c>
-      <c r="W11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" t="s">
-        <v>214</v>
-      </c>
-      <c r="G12" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" t="s">
-        <v>216</v>
-      </c>
-      <c r="I12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" t="s">
-        <v>217</v>
-      </c>
-      <c r="K12" t="s">
-        <v>92</v>
-      </c>
-      <c r="L12" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" t="s">
-        <v>218</v>
-      </c>
-      <c r="O12" t="s">
-        <v>126</v>
-      </c>
-      <c r="P12">
-        <v>214000</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>110</v>
-      </c>
-      <c r="R12" t="s">
-        <v>219</v>
-      </c>
-      <c r="S12" t="s">
-        <v>129</v>
-      </c>
-      <c r="T12" t="s">
-        <v>130</v>
-      </c>
-      <c r="U12" t="s">
-        <v>76</v>
-      </c>
-      <c r="V12" t="s">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s">
-        <v>78</v>
-      </c>
-      <c r="X12" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H13" t="s">
-        <v>226</v>
-      </c>
-      <c r="I13" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K13" t="s">
-        <v>228</v>
-      </c>
-      <c r="L13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13" t="s">
-        <v>61</v>
-      </c>
-      <c r="N13" t="s">
-        <v>229</v>
-      </c>
-      <c r="O13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P13">
-        <v>87300</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>72</v>
-      </c>
-      <c r="R13" t="s">
-        <v>230</v>
-      </c>
-      <c r="S13" t="s">
-        <v>130</v>
-      </c>
-      <c r="T13" t="s">
-        <v>148</v>
-      </c>
-      <c r="U13" t="s">
-        <v>76</v>
-      </c>
-      <c r="V13" t="s">
-        <v>77</v>
-      </c>
-      <c r="W13" t="s">
-        <v>78</v>
-      </c>
-      <c r="X13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z13" t="s">
+      <c r="AK15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AN15" t="s">
         <v>150</v>
       </c>
-      <c r="AA13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>233</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" t="s">
-        <v>235</v>
-      </c>
-      <c r="G14" t="s">
-        <v>236</v>
-      </c>
-      <c r="H14" t="s">
-        <v>237</v>
-      </c>
-      <c r="I14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" t="s">
-        <v>238</v>
-      </c>
-      <c r="K14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L14" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" t="s">
-        <v>61</v>
-      </c>
-      <c r="N14" t="s">
-        <v>240</v>
-      </c>
-      <c r="O14" t="s">
-        <v>162</v>
-      </c>
-      <c r="P14">
-        <v>69900</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>127</v>
-      </c>
-      <c r="R14" t="s">
-        <v>241</v>
-      </c>
-      <c r="S14" t="s">
-        <v>165</v>
-      </c>
-      <c r="T14" t="s">
-        <v>96</v>
-      </c>
-      <c r="U14" t="s">
-        <v>242</v>
-      </c>
-      <c r="V14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W14" t="s">
-        <v>78</v>
-      </c>
-      <c r="X14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>243</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" t="s">
-        <v>245</v>
-      </c>
-      <c r="D15" t="s">
-        <v>246</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" t="s">
-        <v>247</v>
-      </c>
-      <c r="G15" t="s">
-        <v>248</v>
-      </c>
-      <c r="H15" t="s">
-        <v>249</v>
-      </c>
-      <c r="I15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" t="s">
-        <v>250</v>
-      </c>
-      <c r="K15" t="s">
-        <v>251</v>
-      </c>
-      <c r="L15" t="s">
-        <v>252</v>
-      </c>
-      <c r="M15" t="s">
-        <v>253</v>
-      </c>
-      <c r="N15" t="s">
-        <v>254</v>
-      </c>
-      <c r="O15" t="s">
-        <v>109</v>
-      </c>
-      <c r="P15">
-        <v>289500</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>146</v>
-      </c>
-      <c r="R15" t="s">
-        <v>255</v>
-      </c>
-      <c r="S15" t="s">
-        <v>112</v>
-      </c>
-      <c r="T15" t="s">
-        <v>113</v>
-      </c>
-      <c r="U15" t="s">
-        <v>76</v>
-      </c>
-      <c r="V15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W15" t="s">
-        <v>78</v>
-      </c>
-      <c r="X15" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2">
-        <v>120000</v>
-      </c>
-      <c r="E2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" t="s">
-        <v>76</v>
+      <c r="AO15" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/demo-files/tata-capital-bulk-filing-template.xlsx
+++ b/demo-files/tata-capital-bulk-filing-template.xlsx
@@ -490,10 +490,76 @@
     <t>204511</t>
   </si>
   <si>
+    <t>02-09-2026</t>
+  </si>
+  <si>
+    <t>38291004512</t>
+  </si>
+  <si>
+    <t>15-09-2026</t>
+  </si>
+  <si>
+    <t>18-09-2026</t>
+  </si>
+  <si>
+    <t>24-09-2026</t>
+  </si>
+  <si>
+    <t>RG20451111IN</t>
+  </si>
+  <si>
+    <t>02-10-2026</t>
+  </si>
+  <si>
+    <t>Kunal S. Shah</t>
+  </si>
+  <si>
+    <t>Branch Manager, Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>The loan account statement and the dishonour</t>
+  </si>
+  <si>
+    <t>9879055501</t>
+  </si>
+  <si>
+    <t>Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>380009</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1002</t>
+  </si>
+  <si>
+    <t>Snehal K. Mistry</t>
+  </si>
+  <si>
+    <t>9879012302</t>
+  </si>
+  <si>
+    <t>snehal.mistry@mail.example</t>
+  </si>
+  <si>
+    <t>14, Gokul Row Houses, Naranpura</t>
+  </si>
+  <si>
+    <t>380013</t>
+  </si>
+  <si>
+    <t>Naranpura Police Station</t>
+  </si>
+  <si>
+    <t>331207</t>
+  </si>
+  <si>
     <t>01-09-2026</t>
   </si>
   <si>
-    <t>38291004512</t>
+    <t>HDFC0000521</t>
+  </si>
+  <si>
+    <t>50100221834</t>
   </si>
   <si>
     <t>14-09-2026</t>
@@ -505,61 +571,46 @@
     <t>23-09-2026</t>
   </si>
   <si>
-    <t>RG20451111IN</t>
+    <t>RG33120711IN</t>
   </si>
   <si>
     <t>01-10-2026</t>
   </si>
   <si>
-    <t>Kunal S. Shah</t>
-  </si>
-  <si>
-    <t>Branch Manager, Tata Capital, C G Road</t>
-  </si>
-  <si>
-    <t>The loan account statement and the dishonour</t>
-  </si>
-  <si>
-    <t>9879055501</t>
-  </si>
-  <si>
-    <t>Tata Capital, C G Road</t>
-  </si>
-  <si>
-    <t>380009</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1002</t>
-  </si>
-  <si>
-    <t>Snehal K. Mistry</t>
-  </si>
-  <si>
-    <t>9879012302</t>
-  </si>
-  <si>
-    <t>snehal.mistry@mail.example</t>
-  </si>
-  <si>
-    <t>14, Gokul Row Houses, Naranpura</t>
-  </si>
-  <si>
-    <t>380013</t>
-  </si>
-  <si>
-    <t>Naranpura Police Station</t>
-  </si>
-  <si>
-    <t>331207</t>
+    <t>TCL-AHD-BL-1003</t>
+  </si>
+  <si>
+    <t>Pravin D. Solanki</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>9879012303</t>
+  </si>
+  <si>
+    <t>pravin.solanki@mail.example</t>
+  </si>
+  <si>
+    <t>7, Shreeji Society, Maninagar</t>
+  </si>
+  <si>
+    <t>380008</t>
+  </si>
+  <si>
+    <t>Maninagar Police Station</t>
+  </si>
+  <si>
+    <t>118034</t>
   </si>
   <si>
     <t>31-08-2026</t>
   </si>
   <si>
-    <t>HDFC0000521</t>
-  </si>
-  <si>
-    <t>50100221834</t>
+    <t>BARB0MANINA</t>
+  </si>
+  <si>
+    <t>21950100004471</t>
   </si>
   <si>
     <t>13-09-2026</t>
@@ -568,232 +619,181 @@
     <t>16-09-2026</t>
   </si>
   <si>
+    <t>Exceeds arrangement</t>
+  </si>
+  <si>
     <t>22-09-2026</t>
   </si>
   <si>
-    <t>RG33120711IN</t>
+    <t>Speed post</t>
+  </si>
+  <si>
+    <t>RG11803411IN</t>
   </si>
   <si>
     <t>30-09-2026</t>
   </si>
   <si>
-    <t>TCL-AHD-BL-1003</t>
-  </si>
-  <si>
-    <t>Pravin D. Solanki</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>9879012303</t>
-  </si>
-  <si>
-    <t>pravin.solanki@mail.example</t>
-  </si>
-  <si>
-    <t>7, Shreeji Society, Maninagar</t>
-  </si>
-  <si>
-    <t>380008</t>
-  </si>
-  <si>
-    <t>Maninagar Police Station</t>
-  </si>
-  <si>
-    <t>118034</t>
+    <t>Kusum P. Solanki</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>9879012313</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1004</t>
+  </si>
+  <si>
+    <t>Mitali R. Shah</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>9879012304</t>
+  </si>
+  <si>
+    <t>mitali.shah@mail.example</t>
+  </si>
+  <si>
+    <t>C-403, Orchid Greens, Bopal</t>
+  </si>
+  <si>
+    <t>380058</t>
+  </si>
+  <si>
+    <t>Bopal Police Station</t>
+  </si>
+  <si>
+    <t>560921</t>
+  </si>
+  <si>
+    <t>03-09-2026</t>
+  </si>
+  <si>
+    <t>KKBK0002561</t>
+  </si>
+  <si>
+    <t>7612004893</t>
+  </si>
+  <si>
+    <t>19-09-2026</t>
+  </si>
+  <si>
+    <t>Payment stopped by drawer</t>
+  </si>
+  <si>
+    <t>25-09-2026</t>
+  </si>
+  <si>
+    <t>RG56092111IN</t>
+  </si>
+  <si>
+    <t>03-10-2026</t>
+  </si>
+  <si>
+    <t>TCL-AHD-TL-1005</t>
+  </si>
+  <si>
+    <t>Rakesh J. Prajapati</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>9879012305</t>
+  </si>
+  <si>
+    <t>rakesh.prajapati@mail.example</t>
+  </si>
+  <si>
+    <t>33, Shiv Shakti Nagar, Naroda</t>
+  </si>
+  <si>
+    <t>382330</t>
+  </si>
+  <si>
+    <t>Naroda Police Station</t>
+  </si>
+  <si>
+    <t>009812</t>
   </si>
   <si>
     <t>30-08-2026</t>
   </si>
   <si>
-    <t>BARB0MANINA</t>
-  </si>
-  <si>
-    <t>21950100004471</t>
+    <t>PUNB0458600</t>
+  </si>
+  <si>
+    <t>4586000100023911</t>
   </si>
   <si>
     <t>12-09-2026</t>
   </si>
   <si>
-    <t>15-09-2026</t>
-  </si>
-  <si>
-    <t>Exceeds arrangement</t>
-  </si>
-  <si>
     <t>21-09-2026</t>
   </si>
   <si>
-    <t>Speed post</t>
-  </si>
-  <si>
-    <t>RG11803411IN</t>
+    <t>RG00981211IN</t>
   </si>
   <si>
     <t>29-09-2026</t>
   </si>
   <si>
-    <t>Kusum P. Solanki</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>9879012313</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1004</t>
-  </si>
-  <si>
-    <t>Mitali R. Shah</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>9879012304</t>
-  </si>
-  <si>
-    <t>mitali.shah@mail.example</t>
-  </si>
-  <si>
-    <t>C-403, Orchid Greens, Bopal</t>
-  </si>
-  <si>
-    <t>380058</t>
-  </si>
-  <si>
-    <t>Bopal Police Station</t>
-  </si>
-  <si>
-    <t>560921</t>
-  </si>
-  <si>
-    <t>02-09-2026</t>
-  </si>
-  <si>
-    <t>KKBK0002561</t>
-  </si>
-  <si>
-    <t>7612004893</t>
-  </si>
-  <si>
-    <t>18-09-2026</t>
-  </si>
-  <si>
-    <t>Payment stopped by drawer</t>
-  </si>
-  <si>
-    <t>24-09-2026</t>
-  </si>
-  <si>
-    <t>RG56092111IN</t>
-  </si>
-  <si>
-    <t>02-10-2026</t>
-  </si>
-  <si>
-    <t>TCL-AHD-TL-1005</t>
-  </si>
-  <si>
-    <t>Rakesh J. Prajapati</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>9879012305</t>
-  </si>
-  <si>
-    <t>rakesh.prajapati@mail.example</t>
-  </si>
-  <si>
-    <t>33, Shiv Shakti Nagar, Naroda</t>
-  </si>
-  <si>
-    <t>382330</t>
-  </si>
-  <si>
-    <t>Naroda Police Station</t>
-  </si>
-  <si>
-    <t>009812</t>
-  </si>
-  <si>
-    <t>29-08-2026</t>
-  </si>
-  <si>
-    <t>PUNB0458600</t>
-  </si>
-  <si>
-    <t>4586000100023911</t>
-  </si>
-  <si>
-    <t>11-09-2026</t>
+    <t>Unclaimed</t>
+  </si>
+  <si>
+    <t>TCL-AHD-BL-1006</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Sarthak Packaging Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Private limited company</t>
+  </si>
+  <si>
+    <t>9879012306</t>
+  </si>
+  <si>
+    <t>accounts@sarthakpack.example</t>
+  </si>
+  <si>
+    <t>Plot 41, GIDC Phase 2, Naroda</t>
+  </si>
+  <si>
+    <t>Nikhil S. Desai</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>442190</t>
+  </si>
+  <si>
+    <t>04-09-2026</t>
+  </si>
+  <si>
+    <t>UTIB0000080</t>
+  </si>
+  <si>
+    <t>917020045512230</t>
   </si>
   <si>
     <t>20-09-2026</t>
   </si>
   <si>
-    <t>RG00981211IN</t>
-  </si>
-  <si>
-    <t>28-09-2026</t>
-  </si>
-  <si>
-    <t>Unclaimed</t>
-  </si>
-  <si>
-    <t>TCL-AHD-BL-1006</t>
-  </si>
-  <si>
-    <t>Institution</t>
-  </si>
-  <si>
-    <t>Sarthak Packaging Pvt Ltd</t>
-  </si>
-  <si>
-    <t>Private limited company</t>
-  </si>
-  <si>
-    <t>9879012306</t>
-  </si>
-  <si>
-    <t>accounts@sarthakpack.example</t>
-  </si>
-  <si>
-    <t>Plot 41, GIDC Phase 2, Naroda</t>
-  </si>
-  <si>
-    <t>Nikhil S. Desai</t>
-  </si>
-  <si>
-    <t>Managing Director</t>
-  </si>
-  <si>
-    <t>442190</t>
-  </si>
-  <si>
-    <t>03-09-2026</t>
-  </si>
-  <si>
-    <t>UTIB0000080</t>
-  </si>
-  <si>
-    <t>917020045512230</t>
-  </si>
-  <si>
-    <t>19-09-2026</t>
-  </si>
-  <si>
-    <t>25-09-2026</t>
+    <t>26-09-2026</t>
   </si>
   <si>
     <t>RG44219011IN</t>
   </si>
   <si>
-    <t>03-10-2026</t>
+    <t>04-10-2026</t>
   </si>
   <si>
     <t>The loan account statement</t>

--- a/demo-files/tata-capital-bulk-filing-template.xlsx
+++ b/demo-files/tata-capital-bulk-filing-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="342">
   <si>
     <t>Case reference</t>
   </si>
@@ -25,15 +25,15 @@
     <t>Accused institution type</t>
   </si>
   <si>
-    <t>Accused age</t>
-  </si>
-  <si>
     <t>Accused mobile</t>
   </si>
   <si>
     <t>Accused email</t>
   </si>
   <si>
+    <t>Accused resides within jurisdiction</t>
+  </si>
+  <si>
     <t>Accused address</t>
   </si>
   <si>
@@ -79,6 +79,12 @@
     <t>Drawer bank IFSC</t>
   </si>
   <si>
+    <t>Drawer bank name</t>
+  </si>
+  <si>
+    <t>Drawer bank branch</t>
+  </si>
+  <si>
     <t>Drawer account number</t>
   </si>
   <si>
@@ -97,6 +103,12 @@
     <t>Complainant branch IFSC</t>
   </si>
   <si>
+    <t>Complainant bank name</t>
+  </si>
+  <si>
+    <t>Complainant bank branch</t>
+  </si>
+  <si>
     <t>Complainant branch police station</t>
   </si>
   <si>
@@ -169,6 +181,9 @@
     <t>Witness pincode</t>
   </si>
   <si>
+    <t>Witness police station</t>
+  </si>
+  <si>
     <t>Other pending case court</t>
   </si>
   <si>
@@ -220,6 +235,9 @@
     <t>Complainant representative mobile_2</t>
   </si>
   <si>
+    <t>Complainant representative email_2</t>
+  </si>
+  <si>
     <t>Cheque number_2</t>
   </si>
   <si>
@@ -250,9 +268,6 @@
     <t>Accused name_2</t>
   </si>
   <si>
-    <t>Accused age_2</t>
-  </si>
-  <si>
     <t>Accused mobile_2</t>
   </si>
   <si>
@@ -298,90 +313,99 @@
     <t>Choose from the dropdown. Required when Institution</t>
   </si>
   <si>
+    <t>10-digit mobile number. Required: mobile or email</t>
+  </si>
+  <si>
+    <t>Text. Required: mobile or email</t>
+  </si>
+  <si>
+    <t>Choose: Yes / No. Optional</t>
+  </si>
+  <si>
+    <t>Text. Required when Institution</t>
+  </si>
+  <si>
+    <t>Text. Optional</t>
+  </si>
+  <si>
+    <t>10-digit mobile number. Optional</t>
+  </si>
+  <si>
+    <t>Text. Required, 6 digits</t>
+  </si>
+  <si>
+    <t>Date, DD-MM-YYYY. Required</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required</t>
+  </si>
+  <si>
+    <t>Text. Required when the IFSC is not found</t>
+  </si>
+  <si>
+    <t>Choose from the dropdown. Required</t>
+  </si>
+  <si>
+    <t>Choose: Yes / No. Required</t>
+  </si>
+  <si>
+    <t>Text. Required when deposited in own account</t>
+  </si>
+  <si>
+    <t>Text. Required when deposited in own account and the IFSC is not found</t>
+  </si>
+  <si>
+    <t>Text. Required when not deposited in own account</t>
+  </si>
+  <si>
+    <t>Date, DD-MM-YYYY. Required when delivered</t>
+  </si>
+  <si>
+    <t>Date, DD-MM-YYYY. Required when not delivered</t>
+  </si>
+  <si>
+    <t>Choose from the dropdown. Required when not delivered</t>
+  </si>
+  <si>
+    <t>Choose: No payment made / Part payment made. Required</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required when part payment</t>
+  </si>
+  <si>
+    <t>Text. Required when the system computes a delay</t>
+  </si>
+  <si>
+    <t>Text. Required: name or designation, for each witness</t>
+  </si>
+  <si>
     <t>Number, no commas. Optional</t>
   </si>
   <si>
-    <t>10-digit mobile number. Required: mobile or email</t>
-  </si>
-  <si>
-    <t>Text. Required: mobile or email</t>
-  </si>
-  <si>
-    <t>Text. Optional</t>
-  </si>
-  <si>
-    <t>Text. Required when Institution</t>
+    <t>Text. Required for each witness</t>
+  </si>
+  <si>
+    <t>Choose: Individual / Institution. Required for each further complainant</t>
+  </si>
+  <si>
+    <t>Text. Required for each further complainant</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required when Individual</t>
+  </si>
+  <si>
+    <t>Choose: Male / Female / Other. Optional</t>
+  </si>
+  <si>
+    <t>10-digit mobile number. Required when Individual</t>
+  </si>
+  <si>
+    <t>Number, no commas. Required when Institution</t>
   </si>
   <si>
     <t>10-digit mobile number. Required when Institution</t>
   </si>
   <si>
-    <t>Text. Required, 6 digits</t>
-  </si>
-  <si>
-    <t>Date, DD-MM-YYYY. Required</t>
-  </si>
-  <si>
-    <t>Number, no commas. Required</t>
-  </si>
-  <si>
-    <t>Choose from the dropdown. Required</t>
-  </si>
-  <si>
-    <t>Choose: Yes / No. Required</t>
-  </si>
-  <si>
-    <t>Text. Required when deposited in own account</t>
-  </si>
-  <si>
-    <t>Text. Required when not deposited in own account</t>
-  </si>
-  <si>
-    <t>Date, DD-MM-YYYY. Required when delivered</t>
-  </si>
-  <si>
-    <t>Date, DD-MM-YYYY. Required when not delivered</t>
-  </si>
-  <si>
-    <t>Choose from the dropdown. Required when not delivered</t>
-  </si>
-  <si>
-    <t>Choose: No payment made / Part payment made. Required</t>
-  </si>
-  <si>
-    <t>Number, no commas. Required when part payment</t>
-  </si>
-  <si>
-    <t>Text. Required when the system computes a delay</t>
-  </si>
-  <si>
-    <t>Text. Required: name or designation, for each witness</t>
-  </si>
-  <si>
-    <t>10-digit mobile number. Optional</t>
-  </si>
-  <si>
-    <t>Text. Required for each witness</t>
-  </si>
-  <si>
-    <t>Choose: Individual / Institution. Required for each further complainant</t>
-  </si>
-  <si>
-    <t>Text. Required for each further complainant</t>
-  </si>
-  <si>
-    <t>Number, no commas. Required when Individual</t>
-  </si>
-  <si>
-    <t>Choose: Male / Female / Other. Optional</t>
-  </si>
-  <si>
-    <t>10-digit mobile number. Required when Individual</t>
-  </si>
-  <si>
-    <t>Number, no commas. Required when Institution</t>
-  </si>
-  <si>
     <t>EXAMPLE-0001</t>
   </si>
   <si>
@@ -394,9 +418,6 @@
     <t/>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
     <t>9824000000</t>
   </si>
   <si>
@@ -472,9 +493,6 @@
     <t>Harsh V. Bhavsar</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>9879012301</t>
   </si>
   <si>
@@ -490,298 +508,451 @@
     <t>204511</t>
   </si>
   <si>
+    <t>03-09-2026</t>
+  </si>
+  <si>
+    <t>38291004512</t>
+  </si>
+  <si>
+    <t>16-09-2026</t>
+  </si>
+  <si>
+    <t>19-09-2026</t>
+  </si>
+  <si>
+    <t>25-09-2026</t>
+  </si>
+  <si>
+    <t>RG20451111IN</t>
+  </si>
+  <si>
+    <t>03-10-2026</t>
+  </si>
+  <si>
+    <t>Kunal S. Shah</t>
+  </si>
+  <si>
+    <t>Branch Manager, Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>The loan account statement and the dishonour</t>
+  </si>
+  <si>
+    <t>9879055501</t>
+  </si>
+  <si>
+    <t>Tata Capital, C G Road</t>
+  </si>
+  <si>
+    <t>380009</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1002</t>
+  </si>
+  <si>
+    <t>Snehal K. Mistry</t>
+  </si>
+  <si>
+    <t>9879012302</t>
+  </si>
+  <si>
+    <t>snehal.mistry@mail.example</t>
+  </si>
+  <si>
+    <t>14, Gokul Row Houses, Naranpura</t>
+  </si>
+  <si>
+    <t>380013</t>
+  </si>
+  <si>
+    <t>Naranpura Police Station</t>
+  </si>
+  <si>
+    <t>331207</t>
+  </si>
+  <si>
+    <t>14-06-2026</t>
+  </si>
+  <si>
+    <t>HDFC0000521</t>
+  </si>
+  <si>
+    <t>50100221834</t>
+  </si>
+  <si>
+    <t>15-09-2026</t>
+  </si>
+  <si>
+    <t>18-09-2026</t>
+  </si>
+  <si>
+    <t>24-09-2026</t>
+  </si>
+  <si>
+    <t>RG33120711IN</t>
+  </si>
+  <si>
+    <t>02-10-2026</t>
+  </si>
+  <si>
+    <t>TCL-AHD-BL-1003</t>
+  </si>
+  <si>
+    <t>Pravin D. Solanki</t>
+  </si>
+  <si>
+    <t>9879012303</t>
+  </si>
+  <si>
+    <t>pravin.solanki@mail.example</t>
+  </si>
+  <si>
+    <t>7, Shreeji Society, Maninagar</t>
+  </si>
+  <si>
+    <t>380008</t>
+  </si>
+  <si>
+    <t>Maninagar Police Station</t>
+  </si>
+  <si>
+    <t>118034</t>
+  </si>
+  <si>
+    <t>01-09-2026</t>
+  </si>
+  <si>
+    <t>BARB0MANINA</t>
+  </si>
+  <si>
+    <t>21950100004471</t>
+  </si>
+  <si>
+    <t>14-09-2026</t>
+  </si>
+  <si>
+    <t>17-09-2026</t>
+  </si>
+  <si>
+    <t>Exceeds arrangement</t>
+  </si>
+  <si>
+    <t>23-09-2026</t>
+  </si>
+  <si>
+    <t>Speed post</t>
+  </si>
+  <si>
+    <t>RG11803411IN</t>
+  </si>
+  <si>
+    <t>01-10-2026</t>
+  </si>
+  <si>
+    <t>Kusum P. Solanki</t>
+  </si>
+  <si>
+    <t>9879012313</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1004</t>
+  </si>
+  <si>
+    <t>Mitali R. Shah</t>
+  </si>
+  <si>
+    <t>9879012304</t>
+  </si>
+  <si>
+    <t>mitali.shah@mail.example</t>
+  </si>
+  <si>
+    <t>C-403, Orchid Greens, Bopal</t>
+  </si>
+  <si>
+    <t>380058</t>
+  </si>
+  <si>
+    <t>Bopal Police Station</t>
+  </si>
+  <si>
+    <t>560921</t>
+  </si>
+  <si>
+    <t>24-07-2026</t>
+  </si>
+  <si>
+    <t>KKBK0002561</t>
+  </si>
+  <si>
+    <t>7612004893</t>
+  </si>
+  <si>
+    <t>06-08-2026</t>
+  </si>
+  <si>
+    <t>09-08-2026</t>
+  </si>
+  <si>
+    <t>Payment stopped by drawer</t>
+  </si>
+  <si>
+    <t>15-08-2026</t>
+  </si>
+  <si>
+    <t>RG56092111IN</t>
+  </si>
+  <si>
+    <t>23-08-2026</t>
+  </si>
+  <si>
+    <t>TCL-AHD-TL-1005</t>
+  </si>
+  <si>
+    <t>Rakesh J. Prajapati</t>
+  </si>
+  <si>
+    <t>9879012305</t>
+  </si>
+  <si>
+    <t>rakesh.prajapati@mail.example</t>
+  </si>
+  <si>
+    <t>33, Shiv Shakti Nagar, Naroda</t>
+  </si>
+  <si>
+    <t>382330</t>
+  </si>
+  <si>
+    <t>Naroda Police Station</t>
+  </si>
+  <si>
+    <t>009812</t>
+  </si>
+  <si>
+    <t>31-08-2026</t>
+  </si>
+  <si>
+    <t>PUNB0458600</t>
+  </si>
+  <si>
+    <t>4586000100023911</t>
+  </si>
+  <si>
+    <t>13-09-2026</t>
+  </si>
+  <si>
+    <t>22-09-2026</t>
+  </si>
+  <si>
+    <t>RG00981211IN</t>
+  </si>
+  <si>
+    <t>30-09-2026</t>
+  </si>
+  <si>
+    <t>Unclaimed</t>
+  </si>
+  <si>
+    <t>TCL-AHD-BL-1006</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Sarthak Packaging Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Private limited company</t>
+  </si>
+  <si>
+    <t>9879012306</t>
+  </si>
+  <si>
+    <t>accounts@sarthakpack.example</t>
+  </si>
+  <si>
+    <t>Plot 41, GIDC Phase 2, Naroda</t>
+  </si>
+  <si>
+    <t>Nikhil S. Desai</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>442190</t>
+  </si>
+  <si>
+    <t>05-09-2026</t>
+  </si>
+  <si>
+    <t>UTIB0000080</t>
+  </si>
+  <si>
+    <t>917020045512230</t>
+  </si>
+  <si>
+    <t>21-09-2026</t>
+  </si>
+  <si>
+    <t>27-09-2026</t>
+  </si>
+  <si>
+    <t>RG44219011IN</t>
+  </si>
+  <si>
+    <t>05-10-2026</t>
+  </si>
+  <si>
+    <t>The loan account statement</t>
+  </si>
+  <si>
+    <t>Dipti R. Vora</t>
+  </si>
+  <si>
+    <t>Collections Officer</t>
+  </si>
+  <si>
+    <t>Presentation and return of the cheque</t>
+  </si>
+  <si>
+    <t>9879055502</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1007</t>
+  </si>
+  <si>
+    <t>Jayesh M. Rana</t>
+  </si>
+  <si>
+    <t>9879012307</t>
+  </si>
+  <si>
+    <t>jayesh.rana@mail.example</t>
+  </si>
+  <si>
+    <t>9, Sahjanand Park, Paldi</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
+    <t>380006</t>
+  </si>
+  <si>
+    <t>Paldi Police Station</t>
+  </si>
+  <si>
+    <t>671455</t>
+  </si>
+  <si>
+    <t>CNRB0002627</t>
+  </si>
+  <si>
+    <t>2627101009981</t>
+  </si>
+  <si>
+    <t>RG67145511IN</t>
+  </si>
+  <si>
+    <t>Part payment made</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1008</t>
+  </si>
+  <si>
+    <t>Kinjal A. Trivedi</t>
+  </si>
+  <si>
+    <t>9879012308</t>
+  </si>
+  <si>
+    <t>kinjal.trivedi@mail.example</t>
+  </si>
+  <si>
+    <t>A-22, Satyam Tenements, Satellite</t>
+  </si>
+  <si>
+    <t>38001</t>
+  </si>
+  <si>
+    <t>780312</t>
+  </si>
+  <si>
     <t>02-09-2026</t>
   </si>
   <si>
-    <t>38291004512</t>
-  </si>
-  <si>
-    <t>15-09-2026</t>
-  </si>
-  <si>
-    <t>18-09-2026</t>
-  </si>
-  <si>
-    <t>24-09-2026</t>
-  </si>
-  <si>
-    <t>RG20451111IN</t>
-  </si>
-  <si>
-    <t>02-10-2026</t>
-  </si>
-  <si>
-    <t>Kunal S. Shah</t>
-  </si>
-  <si>
-    <t>Branch Manager, Tata Capital, C G Road</t>
-  </si>
-  <si>
-    <t>The loan account statement and the dishonour</t>
-  </si>
-  <si>
-    <t>9879055501</t>
-  </si>
-  <si>
-    <t>Tata Capital, C G Road</t>
-  </si>
-  <si>
-    <t>380009</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1002</t>
-  </si>
-  <si>
-    <t>Snehal K. Mistry</t>
-  </si>
-  <si>
-    <t>9879012302</t>
-  </si>
-  <si>
-    <t>snehal.mistry@mail.example</t>
-  </si>
-  <si>
-    <t>14, Gokul Row Houses, Naranpura</t>
-  </si>
-  <si>
-    <t>380013</t>
-  </si>
-  <si>
-    <t>Naranpura Police Station</t>
-  </si>
-  <si>
-    <t>331207</t>
-  </si>
-  <si>
-    <t>01-09-2026</t>
-  </si>
-  <si>
-    <t>HDFC0000521</t>
-  </si>
-  <si>
-    <t>50100221834</t>
-  </si>
-  <si>
-    <t>14-09-2026</t>
-  </si>
-  <si>
-    <t>17-09-2026</t>
-  </si>
-  <si>
-    <t>23-09-2026</t>
-  </si>
-  <si>
-    <t>RG33120711IN</t>
-  </si>
-  <si>
-    <t>01-10-2026</t>
-  </si>
-  <si>
-    <t>TCL-AHD-BL-1003</t>
-  </si>
-  <si>
-    <t>Pravin D. Solanki</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>9879012303</t>
-  </si>
-  <si>
-    <t>pravin.solanki@mail.example</t>
-  </si>
-  <si>
-    <t>7, Shreeji Society, Maninagar</t>
-  </si>
-  <si>
-    <t>380008</t>
-  </si>
-  <si>
-    <t>Maninagar Police Station</t>
-  </si>
-  <si>
-    <t>118034</t>
-  </si>
-  <si>
-    <t>31-08-2026</t>
-  </si>
-  <si>
-    <t>BARB0MANINA</t>
-  </si>
-  <si>
-    <t>21950100004471</t>
-  </si>
-  <si>
-    <t>13-09-2026</t>
-  </si>
-  <si>
-    <t>16-09-2026</t>
-  </si>
-  <si>
-    <t>Exceeds arrangement</t>
-  </si>
-  <si>
-    <t>22-09-2026</t>
-  </si>
-  <si>
-    <t>Speed post</t>
-  </si>
-  <si>
-    <t>RG11803411IN</t>
-  </si>
-  <si>
-    <t>30-09-2026</t>
-  </si>
-  <si>
-    <t>Kusum P. Solanki</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>9879012313</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1004</t>
-  </si>
-  <si>
-    <t>Mitali R. Shah</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>9879012304</t>
-  </si>
-  <si>
-    <t>mitali.shah@mail.example</t>
-  </si>
-  <si>
-    <t>C-403, Orchid Greens, Bopal</t>
-  </si>
-  <si>
-    <t>380058</t>
-  </si>
-  <si>
-    <t>Bopal Police Station</t>
-  </si>
-  <si>
-    <t>560921</t>
-  </si>
-  <si>
-    <t>03-09-2026</t>
-  </si>
-  <si>
-    <t>KKBK0002561</t>
-  </si>
-  <si>
-    <t>7612004893</t>
-  </si>
-  <si>
-    <t>19-09-2026</t>
-  </si>
-  <si>
-    <t>Payment stopped by drawer</t>
-  </si>
-  <si>
-    <t>25-09-2026</t>
-  </si>
-  <si>
-    <t>RG56092111IN</t>
-  </si>
-  <si>
-    <t>03-10-2026</t>
-  </si>
-  <si>
-    <t>TCL-AHD-TL-1005</t>
-  </si>
-  <si>
-    <t>Rakesh J. Prajapati</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>9879012305</t>
-  </si>
-  <si>
-    <t>rakesh.prajapati@mail.example</t>
-  </si>
-  <si>
-    <t>33, Shiv Shakti Nagar, Naroda</t>
-  </si>
-  <si>
-    <t>382330</t>
-  </si>
-  <si>
-    <t>Naroda Police Station</t>
-  </si>
-  <si>
-    <t>009812</t>
-  </si>
-  <si>
-    <t>30-08-2026</t>
-  </si>
-  <si>
-    <t>PUNB0458600</t>
-  </si>
-  <si>
-    <t>4586000100023911</t>
-  </si>
-  <si>
-    <t>12-09-2026</t>
-  </si>
-  <si>
-    <t>21-09-2026</t>
-  </si>
-  <si>
-    <t>RG00981211IN</t>
-  </si>
-  <si>
-    <t>29-09-2026</t>
-  </si>
-  <si>
-    <t>Unclaimed</t>
-  </si>
-  <si>
-    <t>TCL-AHD-BL-1006</t>
-  </si>
-  <si>
-    <t>Institution</t>
-  </si>
-  <si>
-    <t>Sarthak Packaging Pvt Ltd</t>
-  </si>
-  <si>
-    <t>Private limited company</t>
-  </si>
-  <si>
-    <t>9879012306</t>
-  </si>
-  <si>
-    <t>accounts@sarthakpack.example</t>
-  </si>
-  <si>
-    <t>Plot 41, GIDC Phase 2, Naroda</t>
-  </si>
-  <si>
-    <t>Nikhil S. Desai</t>
-  </si>
-  <si>
-    <t>Managing Director</t>
-  </si>
-  <si>
-    <t>442190</t>
+    <t>ICIC0000317</t>
+  </si>
+  <si>
+    <t>031701509872</t>
+  </si>
+  <si>
+    <t>RG78031211IN</t>
+  </si>
+  <si>
+    <t>TCL-AHD-BL-1009</t>
+  </si>
+  <si>
+    <t>Devang P. Joshi</t>
+  </si>
+  <si>
+    <t>9879012309</t>
+  </si>
+  <si>
+    <t>devang.joshi@mail.example</t>
+  </si>
+  <si>
+    <t>5, Rajpath Bungalows, Bodakdev</t>
+  </si>
+  <si>
+    <t>380054</t>
+  </si>
+  <si>
+    <t>253660</t>
+  </si>
+  <si>
+    <t>50100332918</t>
+  </si>
+  <si>
+    <t>RG25366011IN</t>
+  </si>
+  <si>
+    <t>SARAS Court, Ahmedabad</t>
+  </si>
+  <si>
+    <t>eCC/2210/2026</t>
+  </si>
+  <si>
+    <t>253661</t>
+  </si>
+  <si>
+    <t>TCL-AHD-PL-1010</t>
+  </si>
+  <si>
+    <t>Shree Ganesh Traders</t>
+  </si>
+  <si>
+    <t>9879012310</t>
+  </si>
+  <si>
+    <t>ganesh.traders@mail.example</t>
+  </si>
+  <si>
+    <t>18, Nilkanth Society, Navrangpura</t>
+  </si>
+  <si>
+    <t>Navrangpura Police Station</t>
+  </si>
+  <si>
+    <t>904417</t>
   </si>
   <si>
     <t>04-09-2026</t>
   </si>
   <si>
-    <t>UTIB0000080</t>
-  </si>
-  <si>
-    <t>917020045512230</t>
+    <t>38291007788</t>
   </si>
   <si>
     <t>20-09-2026</t>
@@ -790,178 +961,16 @@
     <t>26-09-2026</t>
   </si>
   <si>
-    <t>RG44219011IN</t>
+    <t>RG90441711IN</t>
   </si>
   <si>
     <t>04-10-2026</t>
   </si>
   <si>
-    <t>The loan account statement</t>
-  </si>
-  <si>
-    <t>Dipti R. Vora</t>
-  </si>
-  <si>
-    <t>Collections Officer</t>
-  </si>
-  <si>
-    <t>Presentation and return of the cheque</t>
-  </si>
-  <si>
-    <t>9879055502</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1007</t>
-  </si>
-  <si>
-    <t>Jayesh M. Rana</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>9879012307</t>
-  </si>
-  <si>
-    <t>jayesh.rana@mail.example</t>
-  </si>
-  <si>
-    <t>9, Sahjanand Park, Paldi</t>
-  </si>
-  <si>
-    <t>Vadodara</t>
-  </si>
-  <si>
-    <t>380006</t>
-  </si>
-  <si>
-    <t>Paldi Police Station</t>
-  </si>
-  <si>
-    <t>671455</t>
-  </si>
-  <si>
-    <t>CNRB0002627</t>
-  </si>
-  <si>
-    <t>2627101009981</t>
-  </si>
-  <si>
-    <t>RG67145511IN</t>
-  </si>
-  <si>
-    <t>Part payment made</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1008</t>
-  </si>
-  <si>
-    <t>Kinjal A. Trivedi</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>9879012308</t>
-  </si>
-  <si>
-    <t>kinjal.trivedi@mail.example</t>
-  </si>
-  <si>
-    <t>A-22, Satyam Tenements, Satellite</t>
-  </si>
-  <si>
-    <t>38001</t>
-  </si>
-  <si>
-    <t>780312</t>
-  </si>
-  <si>
-    <t>ICIC0000317</t>
-  </si>
-  <si>
-    <t>031701509872</t>
-  </si>
-  <si>
-    <t>RG78031211IN</t>
-  </si>
-  <si>
-    <t>TCL-AHD-BL-1009</t>
-  </si>
-  <si>
-    <t>Devang P. Joshi</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>9879012309</t>
-  </si>
-  <si>
-    <t>devang.joshi@mail.example</t>
-  </si>
-  <si>
-    <t>5, Rajpath Bungalows, Bodakdev</t>
-  </si>
-  <si>
-    <t>380054</t>
-  </si>
-  <si>
-    <t>253660</t>
-  </si>
-  <si>
-    <t>50100332918</t>
-  </si>
-  <si>
-    <t>RG25366011IN</t>
-  </si>
-  <si>
-    <t>SARAS Court, Ahmedabad</t>
-  </si>
-  <si>
-    <t>eCC/2210/2026</t>
-  </si>
-  <si>
-    <t>253661</t>
-  </si>
-  <si>
-    <t>TCL-AHD-PL-1010</t>
-  </si>
-  <si>
-    <t>Shree Ganesh Traders</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>9879012310</t>
-  </si>
-  <si>
-    <t>ganesh.traders@mail.example</t>
-  </si>
-  <si>
-    <t>18, Nilkanth Society, Navrangpura</t>
-  </si>
-  <si>
-    <t>Navrangpura Police Station</t>
-  </si>
-  <si>
-    <t>904417</t>
-  </si>
-  <si>
-    <t>38291007788</t>
-  </si>
-  <si>
-    <t>RG90441711IN</t>
-  </si>
-  <si>
     <t>TCL-AHD-TL-1011</t>
   </si>
   <si>
     <t>Imran S. Shaikh</t>
-  </si>
-  <si>
-    <t>39</t>
   </si>
   <si>
     <t>9879012311</t>
@@ -1425,12 +1434,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CM15"/>
+  <dimension ref="A1:CR15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="7" width="18" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="39" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
@@ -1443,72 +1453,77 @@
     <col min="17" max="17" width="27" customWidth="1"/>
     <col min="18" max="18" width="30" customWidth="1"/>
     <col min="19" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="26" width="18" customWidth="1"/>
-    <col min="27" max="27" width="42" customWidth="1"/>
-    <col min="28" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="37" customWidth="1"/>
-    <col min="30" max="30" width="32" customWidth="1"/>
-    <col min="31" max="31" width="18" customWidth="1"/>
-    <col min="32" max="32" width="24" customWidth="1"/>
-    <col min="33" max="34" width="26" customWidth="1"/>
-    <col min="35" max="35" width="20" customWidth="1"/>
+    <col min="22" max="23" width="20" customWidth="1"/>
+    <col min="24" max="24" width="22" customWidth="1"/>
+    <col min="25" max="25" width="25" customWidth="1"/>
+    <col min="26" max="26" width="21" customWidth="1"/>
+    <col min="27" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="42" customWidth="1"/>
+    <col min="30" max="30" width="27" customWidth="1"/>
+    <col min="31" max="31" width="25" customWidth="1"/>
+    <col min="32" max="32" width="27" customWidth="1"/>
+    <col min="33" max="33" width="37" customWidth="1"/>
+    <col min="34" max="34" width="32" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
     <col min="36" max="36" width="24" customWidth="1"/>
-    <col min="37" max="37" width="22" customWidth="1"/>
-    <col min="38" max="38" width="27" customWidth="1"/>
-    <col min="39" max="39" width="19" customWidth="1"/>
+    <col min="37" max="38" width="26" customWidth="1"/>
+    <col min="39" max="39" width="20" customWidth="1"/>
     <col min="40" max="40" width="24" customWidth="1"/>
-    <col min="41" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="35" customWidth="1"/>
-    <col min="43" max="43" width="22" customWidth="1"/>
-    <col min="44" max="44" width="18" customWidth="1"/>
-    <col min="45" max="45" width="23" customWidth="1"/>
-    <col min="46" max="46" width="18" customWidth="1"/>
-    <col min="47" max="47" width="31" customWidth="1"/>
-    <col min="48" max="49" width="18" customWidth="1"/>
-    <col min="50" max="50" width="19" customWidth="1"/>
-    <col min="51" max="51" width="18" customWidth="1"/>
-    <col min="52" max="52" width="19" customWidth="1"/>
-    <col min="53" max="53" width="28" customWidth="1"/>
-    <col min="54" max="54" width="29" customWidth="1"/>
-    <col min="55" max="56" width="22" customWidth="1"/>
-    <col min="57" max="57" width="34" customWidth="1"/>
+    <col min="41" max="41" width="22" customWidth="1"/>
+    <col min="42" max="42" width="27" customWidth="1"/>
+    <col min="43" max="43" width="19" customWidth="1"/>
+    <col min="44" max="44" width="24" customWidth="1"/>
+    <col min="45" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="35" customWidth="1"/>
+    <col min="47" max="47" width="22" customWidth="1"/>
+    <col min="48" max="48" width="18" customWidth="1"/>
+    <col min="49" max="49" width="23" customWidth="1"/>
+    <col min="50" max="50" width="18" customWidth="1"/>
+    <col min="51" max="51" width="31" customWidth="1"/>
+    <col min="52" max="53" width="18" customWidth="1"/>
+    <col min="54" max="54" width="19" customWidth="1"/>
+    <col min="55" max="55" width="18" customWidth="1"/>
+    <col min="56" max="56" width="19" customWidth="1"/>
+    <col min="57" max="57" width="26" customWidth="1"/>
     <col min="58" max="58" width="28" customWidth="1"/>
-    <col min="59" max="59" width="21" customWidth="1"/>
-    <col min="60" max="61" width="24" customWidth="1"/>
-    <col min="62" max="62" width="23" customWidth="1"/>
-    <col min="63" max="63" width="25" customWidth="1"/>
-    <col min="64" max="64" width="22" customWidth="1"/>
-    <col min="65" max="65" width="25" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="44" customWidth="1"/>
-    <col min="68" max="68" width="36" customWidth="1"/>
-    <col min="69" max="69" width="39" customWidth="1"/>
-    <col min="70" max="70" width="19" customWidth="1"/>
-    <col min="71" max="71" width="18" customWidth="1"/>
-    <col min="72" max="72" width="19" customWidth="1"/>
-    <col min="73" max="73" width="22" customWidth="1"/>
-    <col min="74" max="74" width="27" customWidth="1"/>
-    <col min="75" max="75" width="23" customWidth="1"/>
-    <col min="76" max="76" width="18" customWidth="1"/>
-    <col min="77" max="77" width="19" customWidth="1"/>
-    <col min="78" max="80" width="18" customWidth="1"/>
-    <col min="81" max="81" width="20" customWidth="1"/>
-    <col min="82" max="82" width="21" customWidth="1"/>
-    <col min="83" max="83" width="18" customWidth="1"/>
-    <col min="84" max="84" width="21" customWidth="1"/>
-    <col min="85" max="85" width="18" customWidth="1"/>
-    <col min="86" max="86" width="25" customWidth="1"/>
-    <col min="87" max="87" width="33" customWidth="1"/>
-    <col min="88" max="88" width="20" customWidth="1"/>
+    <col min="59" max="59" width="29" customWidth="1"/>
+    <col min="60" max="61" width="22" customWidth="1"/>
+    <col min="62" max="62" width="34" customWidth="1"/>
+    <col min="63" max="63" width="28" customWidth="1"/>
+    <col min="64" max="64" width="21" customWidth="1"/>
+    <col min="65" max="66" width="24" customWidth="1"/>
+    <col min="67" max="67" width="23" customWidth="1"/>
+    <col min="68" max="68" width="25" customWidth="1"/>
+    <col min="69" max="69" width="22" customWidth="1"/>
+    <col min="70" max="70" width="25" customWidth="1"/>
+    <col min="71" max="71" width="37" customWidth="1"/>
+    <col min="72" max="72" width="44" customWidth="1"/>
+    <col min="73" max="73" width="36" customWidth="1"/>
+    <col min="74" max="74" width="39" customWidth="1"/>
+    <col min="75" max="75" width="38" customWidth="1"/>
+    <col min="76" max="76" width="19" customWidth="1"/>
+    <col min="77" max="77" width="18" customWidth="1"/>
+    <col min="78" max="78" width="19" customWidth="1"/>
+    <col min="79" max="79" width="22" customWidth="1"/>
+    <col min="80" max="80" width="27" customWidth="1"/>
+    <col min="81" max="81" width="23" customWidth="1"/>
+    <col min="82" max="82" width="18" customWidth="1"/>
+    <col min="83" max="83" width="19" customWidth="1"/>
+    <col min="84" max="85" width="18" customWidth="1"/>
+    <col min="86" max="86" width="20" customWidth="1"/>
+    <col min="87" max="87" width="21" customWidth="1"/>
+    <col min="88" max="88" width="18" customWidth="1"/>
     <col min="89" max="89" width="21" customWidth="1"/>
     <col min="90" max="90" width="18" customWidth="1"/>
-    <col min="91" max="91" width="21" customWidth="1"/>
+    <col min="91" max="91" width="25" customWidth="1"/>
+    <col min="92" max="92" width="33" customWidth="1"/>
+    <col min="93" max="93" width="20" customWidth="1"/>
+    <col min="94" max="94" width="21" customWidth="1"/>
+    <col min="95" max="95" width="18" customWidth="1"/>
+    <col min="96" max="96" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1782,1851 +1797,1860 @@
       <c r="CM1" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="CN1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
-    <row r="2" spans="1:91" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:96" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>98</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BG2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BI2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="U2" s="3" t="s">
+      <c r="BK2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z2" s="3" t="s">
+      <c r="BL2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AA2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AN2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AR2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AX2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AY2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BG2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BH2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BI2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BJ2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BK2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BO2" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="BP2" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="BQ2" s="3" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="BR2" s="3" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="BS2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BT2" s="3" t="s">
         <v>103</v>
       </c>
       <c r="BU2" s="3" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="BV2" s="3" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="BW2" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BX2" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="BY2" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BZ2" s="3" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="CA2" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="CB2" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="CC2" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="CD2" s="3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="CE2" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="CF2" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="CG2" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="CH2" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="CI2" s="3" t="s">
         <v>98</v>
       </c>
       <c r="CJ2" s="3" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="CK2" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="CL2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="CM2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
+      </c>
+      <c r="CN2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="CO2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="CP2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CQ2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CR2" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:69" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AM3" s="3" t="s">
         <v>149</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AQ3" s="3" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="AS3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AT3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AU3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AV3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AX3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AY3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AZ3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BA3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BB3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BC3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BD3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BE3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BF3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BG3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BH3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BI3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BJ3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BK3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BL3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BM3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BN3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BO3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BQ3" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BS3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BT3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="L4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="T4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="U4">
         <v>148500</v>
       </c>
       <c r="V4" t="s">
-        <v>137</v>
-      </c>
-      <c r="W4" t="s">
-        <v>160</v>
-      </c>
-      <c r="X4" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="Y4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Z4" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="AA4" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>164</v>
+        <v>148</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>150</v>
       </c>
       <c r="AI4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AK4" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL4" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="s">
         <v>149</v>
       </c>
       <c r="AN4" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="AO4" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>156</v>
       </c>
       <c r="AR4" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AS4" t="s">
-        <v>167</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AV4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>170</v>
+        <v>172</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>173</v>
       </c>
       <c r="AY4" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="AZ4" t="s">
-        <v>171</v>
+        <v>175</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>138</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="F5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="T5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="U5">
         <v>92750</v>
       </c>
       <c r="V5" t="s">
-        <v>181</v>
-      </c>
-      <c r="W5" t="s">
-        <v>182</v>
-      </c>
-      <c r="X5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Y5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Z5" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="AA5" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="AB5" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>150</v>
       </c>
       <c r="AI5" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AK5" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL5" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="AM5" t="s">
         <v>149</v>
       </c>
       <c r="AN5" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="AO5" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="T6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="U6">
         <v>365000</v>
       </c>
       <c r="V6" t="s">
-        <v>198</v>
-      </c>
-      <c r="W6" t="s">
-        <v>199</v>
-      </c>
-      <c r="X6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Z6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AA6" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="AB6" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>205</v>
+        <v>207</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>150</v>
       </c>
       <c r="AI6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AK6" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="AL6" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="AM6" t="s">
         <v>149</v>
       </c>
       <c r="AN6" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="AO6" t="s">
-        <v>126</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>207</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>208</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>209</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>193</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>131</v>
+        <v>134</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>134</v>
       </c>
       <c r="CF6" t="s">
-        <v>194</v>
+        <v>132</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>212</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>213</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>198</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>138</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="T7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U7">
         <v>76400</v>
       </c>
       <c r="V7" t="s">
-        <v>220</v>
-      </c>
-      <c r="W7" t="s">
-        <v>221</v>
-      </c>
-      <c r="X7" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="Y7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AA7" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="AB7" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>224</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>150</v>
       </c>
       <c r="AI7" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AK7" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL7" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="AM7" t="s">
         <v>149</v>
       </c>
       <c r="AN7" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AO7" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
-      </c>
-      <c r="G8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="U8">
         <v>58900</v>
       </c>
       <c r="V8" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>151</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>243</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>244</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>245</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>246</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:96" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" t="s">
+        <v>252</v>
+      </c>
+      <c r="H9" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" t="s">
+        <v>236</v>
+      </c>
+      <c r="K9" t="s">
         <v>237</v>
       </c>
-      <c r="W8" t="s">
-        <v>238</v>
-      </c>
-      <c r="X8" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>241</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>242</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>243</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>149</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>150</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" t="s">
-        <v>131</v>
-      </c>
-      <c r="J9" t="s">
-        <v>233</v>
-      </c>
-      <c r="K9" t="s">
-        <v>234</v>
-      </c>
       <c r="L9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="S9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="T9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="U9">
         <v>512000</v>
       </c>
       <c r="V9" t="s">
-        <v>255</v>
-      </c>
-      <c r="W9" t="s">
-        <v>256</v>
-      </c>
-      <c r="X9" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="Y9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z9" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="AA9" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="AB9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>259</v>
+        <v>148</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>150</v>
       </c>
       <c r="AI9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AK9" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="AL9" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
       <c r="AM9" t="s">
         <v>149</v>
       </c>
       <c r="AN9" t="s">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="AO9" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>156</v>
       </c>
       <c r="AR9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AS9" t="s">
-        <v>167</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="AV9" t="s">
-        <v>169</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>170</v>
+        <v>172</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>173</v>
       </c>
       <c r="AY9" t="s">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="AZ9" t="s">
-        <v>171</v>
-      </c>
-      <c r="CG9" t="s">
-        <v>262</v>
-      </c>
-      <c r="CH9" t="s">
-        <v>263</v>
-      </c>
-      <c r="CI9" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ9" t="s">
+        <v>175</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>138</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>177</v>
+      </c>
+      <c r="CL9" t="s">
         <v>265</v>
       </c>
-      <c r="CK9" t="s">
-        <v>170</v>
-      </c>
-      <c r="CL9" t="s">
-        <v>131</v>
-      </c>
       <c r="CM9" t="s">
-        <v>171</v>
+        <v>266</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>267</v>
+      </c>
+      <c r="CO9" t="s">
+        <v>268</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>176</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>138</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
-      </c>
-      <c r="G10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L10" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="T10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="U10">
         <v>133250</v>
       </c>
       <c r="V10" t="s">
-        <v>276</v>
-      </c>
-      <c r="W10" t="s">
-        <v>277</v>
-      </c>
-      <c r="X10" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="Y10" t="s">
-        <v>162</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="AA10" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="AB10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>278</v>
+        <v>148</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>150</v>
       </c>
       <c r="AI10" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AK10" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL10" t="s">
-        <v>126</v>
+        <v>280</v>
       </c>
       <c r="AM10" t="s">
         <v>149</v>
       </c>
       <c r="AN10" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO10">
+        <v>171</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>281</v>
+      </c>
+      <c r="AS10">
         <v>25000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K11" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="T11" t="s">
-        <v>180</v>
+        <v>289</v>
       </c>
       <c r="U11">
         <v>64800</v>
       </c>
       <c r="V11" t="s">
-        <v>288</v>
-      </c>
-      <c r="W11" t="s">
-        <v>289</v>
-      </c>
-      <c r="X11" t="s">
-        <v>183</v>
+        <v>290</v>
       </c>
       <c r="Y11" t="s">
-        <v>184</v>
+        <v>291</v>
       </c>
       <c r="Z11" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="AA11" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="AB11" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>290</v>
+        <v>148</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>150</v>
       </c>
       <c r="AI11" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AK11" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s">
-        <v>126</v>
+        <v>292</v>
       </c>
       <c r="AM11" t="s">
         <v>149</v>
       </c>
       <c r="AN11" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="AO11" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:77" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
-      </c>
-      <c r="G12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K12" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="T12" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="U12">
         <v>214000</v>
       </c>
       <c r="V12" t="s">
-        <v>181</v>
-      </c>
-      <c r="W12" t="s">
-        <v>299</v>
-      </c>
-      <c r="X12" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="Y12" t="s">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="Z12" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="AA12" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="AB12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>300</v>
+        <v>148</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>150</v>
       </c>
       <c r="AI12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AK12" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="AL12" t="s">
-        <v>126</v>
+        <v>301</v>
       </c>
       <c r="AM12" t="s">
         <v>149</v>
       </c>
       <c r="AN12" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="AO12" t="s">
-        <v>126</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>301</v>
-      </c>
-      <c r="BB12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF12" t="s">
         <v>302</v>
       </c>
-      <c r="BR12" t="s">
+      <c r="BG12" t="s">
         <v>303</v>
       </c>
-      <c r="BS12" t="s">
-        <v>197</v>
-      </c>
-      <c r="BT12">
+      <c r="BX12" t="s">
+        <v>304</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>202</v>
+      </c>
+      <c r="BZ12">
         <v>120000</v>
       </c>
-      <c r="BU12" t="s">
-        <v>181</v>
-      </c>
-      <c r="BV12" t="s">
-        <v>299</v>
-      </c>
-      <c r="BW12" t="s">
-        <v>200</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>201</v>
-      </c>
-      <c r="BY12" t="s">
-        <v>141</v>
+      <c r="CA12" t="s">
+        <v>187</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>300</v>
+      </c>
+      <c r="CC12" t="s">
+        <v>205</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>206</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F13" t="s">
-        <v>307</v>
-      </c>
-      <c r="G13" t="s">
         <v>308</v>
       </c>
       <c r="H13" t="s">
         <v>309</v>
       </c>
       <c r="I13" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K13" t="s">
         <v>310</v>
       </c>
       <c r="L13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S13" t="s">
         <v>311</v>
       </c>
       <c r="T13" t="s">
-        <v>219</v>
+        <v>312</v>
       </c>
       <c r="U13">
         <v>87300</v>
       </c>
       <c r="V13" t="s">
-        <v>137</v>
-      </c>
-      <c r="W13" t="s">
-        <v>312</v>
-      </c>
-      <c r="X13" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="Y13" t="s">
-        <v>222</v>
+        <v>313</v>
       </c>
       <c r="Z13" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="AA13" t="s">
-        <v>142</v>
+        <v>314</v>
       </c>
       <c r="AB13" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>313</v>
+        <v>148</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>150</v>
       </c>
       <c r="AI13" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="AK13" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s">
-        <v>126</v>
+        <v>316</v>
       </c>
       <c r="AM13" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AN13" t="s">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="AO13" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F14" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J14" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L14" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="U14">
         <v>69900</v>
       </c>
       <c r="V14" t="s">
-        <v>198</v>
-      </c>
-      <c r="W14" t="s">
-        <v>323</v>
-      </c>
-      <c r="X14" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="Y14" t="s">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="Z14" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="AA14" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="AB14" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>240</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>325</v>
+        <v>327</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>150</v>
       </c>
       <c r="AI14" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AK14" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL14" t="s">
-        <v>126</v>
+        <v>328</v>
       </c>
       <c r="AM14" t="s">
         <v>149</v>
       </c>
       <c r="AN14" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="AO14" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>332</v>
       </c>
       <c r="F15" t="s">
-        <v>329</v>
-      </c>
-      <c r="G15" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H15" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I15" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="S15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="T15" t="s">
-        <v>180</v>
+        <v>289</v>
       </c>
       <c r="U15">
         <v>289500</v>
       </c>
       <c r="V15" t="s">
-        <v>220</v>
-      </c>
-      <c r="W15" t="s">
-        <v>337</v>
-      </c>
-      <c r="X15" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="Y15" t="s">
-        <v>184</v>
+        <v>340</v>
       </c>
       <c r="Z15" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>338</v>
+        <v>148</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>150</v>
       </c>
       <c r="AI15" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AJ15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AK15" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="AL15" t="s">
-        <v>126</v>
+        <v>341</v>
       </c>
       <c r="AM15" t="s">
         <v>149</v>
       </c>
       <c r="AN15" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="AO15" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
